--- a/LISTAS_ORDENADAS/MI/Tornillos Pitones Arandelas Tuercas/TIRAFONDOS.xlsx
+++ b/LISTAS_ORDENADAS/MI/Tornillos Pitones Arandelas Tuercas/TIRAFONDOS.xlsx
@@ -851,14 +851,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="15" t="n">
-        <v>45211.54071571207</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="14">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -880,8 +876,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="14">
       <c r="A11" s="16" t="inlineStr">
         <is>
@@ -896,17 +890,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
     <row r="24" ht="48.75" customHeight="1" s="14"/>
     <row r="25" ht="48.75" customHeight="1" s="14"/>
     <row r="26" ht="48.75" customHeight="1" s="14"/>
@@ -960,7 +943,7 @@
       </c>
       <c r="C32" s="12" t="n"/>
       <c r="D32" s="6" t="n">
-        <v>1202.959</v>
+        <v>1134.867</v>
       </c>
       <c r="E32" s="2" t="n"/>
     </row>
@@ -977,7 +960,7 @@
       </c>
       <c r="C33" s="12" t="n"/>
       <c r="D33" s="6" t="n">
-        <v>1433.094</v>
+        <v>1351.975</v>
       </c>
       <c r="E33" s="2" t="n"/>
     </row>
@@ -994,7 +977,7 @@
       </c>
       <c r="C34" s="12" t="n"/>
       <c r="D34" s="6" t="n">
-        <v>1605.694</v>
+        <v>1514.806</v>
       </c>
       <c r="E34" s="2" t="n"/>
     </row>
@@ -1011,7 +994,7 @@
       </c>
       <c r="C35" s="12" t="n"/>
       <c r="D35" s="7" t="n">
-        <v>1730.007</v>
+        <v>1632.082</v>
       </c>
       <c r="E35" s="2" t="n"/>
     </row>
@@ -1028,7 +1011,7 @@
       </c>
       <c r="C36" s="12" t="n"/>
       <c r="D36" s="6" t="n">
-        <v>1834.62</v>
+        <v>1730.774</v>
       </c>
       <c r="E36" s="2" t="n"/>
     </row>
@@ -1045,7 +1028,7 @@
       </c>
       <c r="C37" s="12" t="n"/>
       <c r="D37" s="7" t="n">
-        <v>2059.915</v>
+        <v>1943.316</v>
       </c>
       <c r="E37" s="2" t="n"/>
     </row>
@@ -1062,7 +1045,7 @@
       </c>
       <c r="C38" s="12" t="n"/>
       <c r="D38" s="6" t="n">
-        <v>2261.083</v>
+        <v>2133.097</v>
       </c>
       <c r="E38" s="2" t="n"/>
     </row>
@@ -1079,7 +1062,7 @@
       </c>
       <c r="C39" s="12" t="n"/>
       <c r="D39" s="7" t="n">
-        <v>2426.033</v>
+        <v>2288.71</v>
       </c>
       <c r="E39" s="2" t="n"/>
     </row>
@@ -1096,7 +1079,7 @@
       </c>
       <c r="C40" s="12" t="n"/>
       <c r="D40" s="6" t="n">
-        <v>2558.804</v>
+        <v>2413.966</v>
       </c>
       <c r="E40" s="2" t="n"/>
     </row>
@@ -1149,7 +1132,7 @@
       </c>
       <c r="C46" s="12" t="n"/>
       <c r="D46" s="7" t="n">
-        <v>1516.781</v>
+        <v>1430.925</v>
       </c>
       <c r="E46" s="2" t="n"/>
     </row>
@@ -1166,7 +1149,7 @@
       </c>
       <c r="C47" s="12" t="n"/>
       <c r="D47" s="7" t="n">
-        <v>1694.605</v>
+        <v>1598.684</v>
       </c>
       <c r="E47" s="2" t="n"/>
     </row>
@@ -1183,7 +1166,7 @@
       </c>
       <c r="C48" s="12" t="n"/>
       <c r="D48" s="7" t="n">
-        <v>1859.57</v>
+        <v>1754.311</v>
       </c>
       <c r="E48" s="2" t="n"/>
     </row>
@@ -1200,7 +1183,7 @@
       </c>
       <c r="C49" s="12" t="n"/>
       <c r="D49" s="7" t="n">
-        <v>2165.327</v>
+        <v>2042.761</v>
       </c>
       <c r="E49" s="2" t="n"/>
     </row>
@@ -1217,7 +1200,7 @@
       </c>
       <c r="C50" s="12" t="n"/>
       <c r="D50" s="7" t="n">
-        <v>2361.67</v>
+        <v>3200</v>
       </c>
       <c r="E50" s="2" t="n"/>
     </row>
@@ -1234,7 +1217,7 @@
       </c>
       <c r="C51" s="12" t="n"/>
       <c r="D51" s="7" t="n">
-        <v>2627.2</v>
+        <v>2478.491</v>
       </c>
       <c r="E51" s="2" t="n"/>
     </row>
@@ -1251,7 +1234,7 @@
       </c>
       <c r="C52" s="12" t="n"/>
       <c r="D52" s="7" t="n">
-        <v>2957.113</v>
+        <v>2789.729</v>
       </c>
       <c r="E52" s="2" t="n"/>
     </row>
@@ -1268,7 +1251,7 @@
       </c>
       <c r="C53" s="12" t="n"/>
       <c r="D53" s="7" t="n">
-        <v>3077.812</v>
+        <v>2903.596</v>
       </c>
       <c r="E53" s="2" t="n"/>
     </row>
@@ -1285,7 +1268,7 @@
       </c>
       <c r="C54" s="12" t="n"/>
       <c r="D54" s="7" t="n">
-        <v>3399.672</v>
+        <v>3207.238</v>
       </c>
       <c r="E54" s="2" t="n"/>
     </row>
@@ -1302,7 +1285,7 @@
       </c>
       <c r="C55" s="12" t="n"/>
       <c r="D55" s="7" t="n">
-        <v>3802.004</v>
+        <v>3586.796</v>
       </c>
       <c r="E55" s="2" t="n"/>
     </row>
@@ -1319,7 +1302,7 @@
       </c>
       <c r="C56" s="12" t="n"/>
       <c r="D56" s="7" t="n">
-        <v>4123.87</v>
+        <v>3890.443</v>
       </c>
       <c r="E56" s="2" t="n"/>
     </row>
@@ -1336,7 +1319,7 @@
       </c>
       <c r="C57" s="12" t="n"/>
       <c r="D57" s="7" t="n">
-        <v>4626.771</v>
+        <v>4364.878</v>
       </c>
       <c r="E57" s="2" t="n"/>
     </row>
@@ -1353,7 +1336,7 @@
       </c>
       <c r="C58" s="12" t="n"/>
       <c r="D58" s="7" t="n">
-        <v>5069.333</v>
+        <v>4782.39</v>
       </c>
       <c r="E58" s="2" t="n"/>
     </row>
@@ -1370,7 +1353,7 @@
       </c>
       <c r="C59" s="12" t="n"/>
       <c r="D59" s="7" t="n">
-        <v>5572.244</v>
+        <v>5256.834</v>
       </c>
       <c r="E59" s="2" t="n"/>
     </row>
@@ -1387,7 +1370,7 @@
       </c>
       <c r="C60" s="12" t="n"/>
       <c r="D60" s="7" t="n">
-        <v>8529.358</v>
+        <v>8046.564</v>
       </c>
       <c r="E60" s="2" t="n"/>
     </row>
@@ -1404,7 +1387,7 @@
       </c>
       <c r="C61" s="12" t="n"/>
       <c r="D61" s="7" t="n">
-        <v>9052.384</v>
+        <v>8539.985000000001</v>
       </c>
       <c r="E61" s="2" t="n"/>
     </row>
@@ -1457,7 +1440,7 @@
       </c>
       <c r="C67" s="12" t="n"/>
       <c r="D67" s="7" t="n">
-        <v>2715.715</v>
+        <v>2561.995</v>
       </c>
       <c r="E67" s="2" t="n"/>
     </row>
@@ -1474,7 +1457,7 @@
       </c>
       <c r="C68" s="12" t="n"/>
       <c r="D68" s="7" t="n">
-        <v>3093.905</v>
+        <v>2918.778</v>
       </c>
       <c r="E68" s="2" t="n"/>
     </row>
@@ -1491,7 +1474,7 @@
       </c>
       <c r="C69" s="12" t="n"/>
       <c r="D69" s="7" t="n">
-        <v>3335.302</v>
+        <v>3146.511</v>
       </c>
       <c r="E69" s="2" t="n"/>
     </row>
@@ -1508,7 +1491,7 @@
       </c>
       <c r="C70" s="12" t="n"/>
       <c r="D70" s="7" t="n">
-        <v>3391.629</v>
+        <v>3199.65</v>
       </c>
       <c r="E70" s="2" t="n"/>
     </row>
@@ -1525,7 +1508,7 @@
       </c>
       <c r="C71" s="12" t="n"/>
       <c r="D71" s="7" t="n">
-        <v>3818.097</v>
+        <v>3601.978</v>
       </c>
       <c r="E71" s="2" t="n"/>
     </row>
@@ -1542,7 +1525,7 @@
       </c>
       <c r="C72" s="12" t="n"/>
       <c r="D72" s="7" t="n">
-        <v>4119.032</v>
+        <v>3885.879</v>
       </c>
       <c r="E72" s="2" t="n"/>
     </row>
@@ -1559,7 +1542,7 @@
       </c>
       <c r="C73" s="12" t="n"/>
       <c r="D73" s="7" t="n">
-        <v>4590.566</v>
+        <v>4330.723</v>
       </c>
       <c r="E73" s="2" t="n"/>
     </row>
@@ -1576,7 +1559,7 @@
       </c>
       <c r="C74" s="12" t="n"/>
       <c r="D74" s="7" t="n">
-        <v>4928.525</v>
+        <v>4649.552</v>
       </c>
       <c r="E74" s="2" t="n"/>
     </row>
@@ -1593,7 +1576,7 @@
       </c>
       <c r="C75" s="12" t="n"/>
       <c r="D75" s="7" t="n">
-        <v>5733.174</v>
+        <v>5408.655</v>
       </c>
       <c r="E75" s="2" t="n"/>
     </row>
@@ -1610,7 +1593,7 @@
       </c>
       <c r="C76" s="12" t="n"/>
       <c r="D76" s="7" t="n">
-        <v>6219.996</v>
+        <v>5867.921</v>
       </c>
       <c r="E76" s="2" t="n"/>
     </row>
@@ -1627,7 +1610,7 @@
       </c>
       <c r="C77" s="12" t="n"/>
       <c r="D77" s="7" t="n">
-        <v>6920.049</v>
+        <v>6528.348</v>
       </c>
       <c r="E77" s="2" t="n"/>
     </row>
@@ -1644,7 +1627,7 @@
       </c>
       <c r="C78" s="12" t="n"/>
       <c r="D78" s="7" t="n">
-        <v>7624.116</v>
+        <v>7192.562</v>
       </c>
       <c r="E78" s="2" t="n"/>
     </row>
@@ -1661,7 +1644,7 @@
       </c>
       <c r="C79" s="12" t="n"/>
       <c r="D79" s="7" t="n">
-        <v>8452.91</v>
+        <v>7974.443</v>
       </c>
       <c r="E79" s="2" t="n"/>
     </row>
@@ -1678,7 +1661,7 @@
       </c>
       <c r="C80" s="12" t="n"/>
       <c r="D80" s="7" t="n">
-        <v>11667.52</v>
+        <v>11007.094</v>
       </c>
       <c r="E80" s="2" t="n"/>
     </row>
@@ -1695,7 +1678,7 @@
       </c>
       <c r="C81" s="12" t="n"/>
       <c r="D81" s="7" t="n">
-        <v>12995.196</v>
+        <v>12259.619</v>
       </c>
       <c r="E81" s="2" t="n"/>
     </row>
@@ -1748,7 +1731,7 @@
       </c>
       <c r="C87" s="12" t="n"/>
       <c r="D87" s="7" t="n">
-        <v>4827.934</v>
+        <v>4554.655</v>
       </c>
       <c r="E87" s="2" t="n"/>
     </row>
@@ -1765,7 +1748,7 @@
       </c>
       <c r="C88" s="12" t="n"/>
       <c r="D88" s="7" t="n">
-        <v>4988.87</v>
+        <v>4706.481</v>
       </c>
       <c r="E88" s="2" t="n"/>
     </row>
@@ -1782,7 +1765,7 @@
       </c>
       <c r="C89" s="12" t="n"/>
       <c r="D89" s="7" t="n">
-        <v>5833.756</v>
+        <v>5503.543</v>
       </c>
       <c r="E89" s="2" t="n"/>
     </row>
@@ -1799,7 +1782,7 @@
       </c>
       <c r="C90" s="12" t="n"/>
       <c r="D90" s="7" t="n">
-        <v>6397.015</v>
+        <v>6034.92</v>
       </c>
       <c r="E90" s="2" t="n"/>
     </row>
@@ -1816,7 +1799,7 @@
       </c>
       <c r="C91" s="12" t="n"/>
       <c r="D91" s="7" t="n">
-        <v>7040.742</v>
+        <v>6642.209</v>
       </c>
       <c r="E91" s="2" t="n"/>
     </row>
@@ -1833,7 +1816,7 @@
       </c>
       <c r="C92" s="12" t="n"/>
       <c r="D92" s="7" t="n">
-        <v>8609.826999999999</v>
+        <v>8122.478</v>
       </c>
       <c r="E92" s="2" t="n"/>
     </row>
@@ -1850,7 +1833,7 @@
       </c>
       <c r="C93" s="12" t="n"/>
       <c r="D93" s="7" t="n">
-        <v>8951.806</v>
+        <v>8445.1</v>
       </c>
       <c r="E93" s="2" t="n"/>
     </row>
@@ -1867,7 +1850,7 @@
       </c>
       <c r="C94" s="12" t="n"/>
       <c r="D94" s="7" t="n">
-        <v>9937.504999999999</v>
+        <v>9375.004999999999</v>
       </c>
       <c r="E94" s="2" t="n"/>
     </row>
@@ -1884,7 +1867,7 @@
       </c>
       <c r="C95" s="12" t="n"/>
       <c r="D95" s="7" t="n">
-        <v>10903.094</v>
+        <v>10285.938</v>
       </c>
       <c r="E95" s="2" t="n"/>
     </row>
@@ -1901,12 +1884,10 @@
       </c>
       <c r="C96" s="12" t="n"/>
       <c r="D96" s="7" t="n">
-        <v>12069.842</v>
+        <v>11386.643</v>
       </c>
       <c r="E96" s="2" t="n"/>
     </row>
-    <row r="97"/>
-    <row r="98"/>
     <row r="99" ht="19.5" customHeight="1" s="14">
       <c r="A99" s="9" t="inlineStr">
         <is>
@@ -1916,68 +1897,68 @@
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="A85:C85"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="A65:C65"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
     <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="A85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
